--- a/Result/profitability/1515.xlsx
+++ b/Result/profitability/1515.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.97</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.004999999999999949</v>
+        <v>-0.003749999999999962</v>
       </c>
       <c r="N2" t="n">
-        <v>13.43375</v>
+        <v>13.295</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.97</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.13125</v>
+        <v>-0.105</v>
       </c>
       <c r="N3" t="n">
-        <v>12.97125</v>
+        <v>13.15125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.36</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1562499999999999</v>
+        <v>-0.1587499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>12.4775</v>
+        <v>12.4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.15</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.30875</v>
+        <v>-0.2437499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>12.72</v>
+        <v>12.69625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2424999999999999</v>
+        <v>-0.2762499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>14.43125</v>
+        <v>14.6825</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.08</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2724999999999999</v>
+        <v>-0.3987499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>16.1975</v>
+        <v>16.17375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.31</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3662499999999999</v>
+        <v>-0.3687499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>18.69375</v>
+        <v>18.48</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.11</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.06249999999999997</v>
+        <v>-0.06249999999999996</v>
       </c>
       <c r="N11" t="n">
         <v>23.3575</v>
@@ -1899,7 +1899,7 @@
         <v>0.26</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01500000000000003</v>
+        <v>0.01500000000000004</v>
       </c>
       <c r="N12" t="n">
         <v>25.58875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1019</v>
+      </c>
+      <c r="E75" t="n">
+        <v>153</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-23</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>40</v>
+      </c>
+      <c r="J75" t="n">
+        <v>16</v>
+      </c>
+      <c r="K75" t="n">
+        <v>9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.07625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.710000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.116010854816825</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.106382978723404</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.1900000000000013</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01437216338880498</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
